--- a/ET-release8.1/Unity/Assets/Config/Excel/MailConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MailConfig.xlsx
@@ -585,7 +585,7 @@
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
-        <v>8800001</v>
+        <v>88001</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -605,7 +605,7 @@
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
-        <v>8800002</v>
+        <v>88002</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
-        <v>8800003</v>
+        <v>88003</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -645,7 +645,7 @@
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
-        <v>8800004</v>
+        <v>88004</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
-        <v>8800005</v>
+        <v>88005</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
